--- a/livros_e_imagens.xlsx
+++ b/livros_e_imagens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Helmer\Documents\py\templates automação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0662995-FC40-429B-80C7-17A95389FC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FE558C-E2B6-4910-8AB7-71827B00E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="870" windowWidth="19860" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="selecao" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="710">
   <si>
     <t>TRANSFORMAÇÃO E CRISE NA ECONOMIA MUNDIAL</t>
   </si>
@@ -2154,22 +2154,19 @@
     <t>imagens</t>
   </si>
   <si>
-    <t>harry potter e a ordem da fenix</t>
-  </si>
-  <si>
-    <t>capitaes da areia</t>
-  </si>
-  <si>
-    <t>a moreninha</t>
-  </si>
-  <si>
-    <t>https://images-na.ssl-images-amazon.com/images/S/compressed.photo.goodreads.com/books/1483087223i/334246.jpg</t>
-  </si>
-  <si>
-    <t>https://livrofacil.vteximg.com.br/arquivos/ids/176531-1000-1000/9788532530820.jpg?v=636735366531800000</t>
-  </si>
-  <si>
-    <t>https://th.bing.com/th/id/R.b0aff56e4135e874148bd59b6bebe384?rik=uGYGW1MRsJhbYQ&amp;pid=ImgRaw&amp;r=0</t>
+    <t>https://th.bing.com/th/id/OIP.WZ8rTvtmR-yPrkV2Grd9iAHaL3?rs=1&amp;pid=ImgDetMain</t>
+  </si>
+  <si>
+    <t>a senhora do jogo</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/R.8cf56f5595b2e94ca02552288add200a?rik=z00AYtCnnK11vQ&amp;pid=ImgRaw&amp;r=0</t>
+  </si>
+  <si>
+    <t>https://cdl-static.s3-sa-east-1.amazonaws.com/covers/gg/9788539008124/pensamento-eficaz.jpg</t>
+  </si>
+  <si>
+    <t>Pensamento Eficaz autor: shane parrish</t>
   </si>
 </sst>
 </file>
@@ -2684,11 +2681,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>705</v>
-      </c>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="9" t="s">
         <v>709</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2696,23 +2693,18 @@
         <v>706</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>707</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>708</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{EA093ABE-BCF8-4C8B-90F0-5DF71C84B3F8}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{8DC7C1B8-0394-4DF1-8D89-FFB94FAAF38D}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{90E7A3E5-20D4-4285-BDC3-E8A1D7D9636C}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
